--- a/data/trans_orig/P19E-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P19E-Estudios-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces que se cepilla los dientes al día en 2016</t>
+          <t>Población según el número de veces que se cepilla los dientes al día en 2016 (tasa de respuesta: 97,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>136972</t>
+          <t>137871</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>180268</t>
+          <t>179993</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>241550</t>
+          <t>245809</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>299743</t>
+          <t>303897</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>396456</t>
+          <t>394249</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>470911</t>
+          <t>468606</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,15%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>158470</t>
+          <t>157363</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>205547</t>
+          <t>204521</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>269247</t>
+          <t>268290</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>325853</t>
+          <t>327803</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>438744</t>
+          <t>437652</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>514801</t>
+          <t>513448</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,84%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>194397</t>
+          <t>192708</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>244598</t>
+          <t>240558</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>219779</t>
+          <t>219366</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>275318</t>
+          <t>274151</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>431495</t>
+          <t>431145</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>500948</t>
+          <t>506276</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,41%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33805</t>
+          <t>33998</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60180</t>
+          <t>59622</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32583</t>
+          <t>31861</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58889</t>
+          <t>58948</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72097</t>
+          <t>71239</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109908</t>
+          <t>110579</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>93374</t>
+          <t>94074</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>132211</t>
+          <t>133826</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73129</t>
+          <t>71246</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>111916</t>
+          <t>109978</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>177588</t>
+          <t>177476</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>229822</t>
+          <t>230813</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>674311</t>
+          <t>674889</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>758511</t>
+          <t>762645</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>838749</t>
+          <t>836611</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>930062</t>
+          <t>923280</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1537914</t>
+          <t>1536235</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1663455</t>
+          <t>1663348</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,83%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>609178</t>
+          <t>610899</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>699105</t>
+          <t>694688</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>637173</t>
+          <t>638461</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>720562</t>
+          <t>722542</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1273950</t>
+          <t>1272247</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1398120</t>
+          <t>1389627</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>34,95%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>447182</t>
+          <t>449304</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>531128</t>
+          <t>529050</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>306686</t>
+          <t>309050</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>375903</t>
+          <t>379182</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>774334</t>
+          <t>782187</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>883053</t>
+          <t>881785</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34534</t>
+          <t>33787</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62986</t>
+          <t>62461</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10666</t>
+          <t>10322</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31460</t>
+          <t>29875</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50106</t>
+          <t>49947</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85320</t>
+          <t>85709</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>100980</t>
+          <t>101033</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>146320</t>
+          <t>146676</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18686</t>
+          <t>19031</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40229</t>
+          <t>40378</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>124820</t>
+          <t>126356</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>176127</t>
+          <t>178225</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>253851</t>
+          <t>253826</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>301915</t>
+          <t>304289</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>310663</t>
+          <t>310419</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>356349</t>
+          <t>357080</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>580811</t>
+          <t>577582</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>643668</t>
+          <t>646764</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,69%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>129070</t>
+          <t>131284</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>172908</t>
+          <t>174836</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>131563</t>
+          <t>131419</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>174698</t>
+          <t>175247</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>274295</t>
+          <t>275645</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>334173</t>
+          <t>336406</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,05%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>78328</t>
+          <t>78101</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>115074</t>
+          <t>115222</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38879</t>
+          <t>38624</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>66943</t>
+          <t>66774</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>124536</t>
+          <t>124950</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>171694</t>
+          <t>170365</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1508</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12097</t>
+          <t>12771</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14107</t>
+          <t>13181</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3756</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16303</t>
+          <t>15738</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>11448</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6819</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21957</t>
+          <t>23043</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1098243</t>
+          <t>1097780</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1209711</t>
+          <t>1208958</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1428062</t>
+          <t>1426649</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1547293</t>
+          <t>1542506</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2573048</t>
+          <t>2557344</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2724518</t>
+          <t>2724260</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,51%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>932158</t>
+          <t>935033</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1040437</t>
+          <t>1036217</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1071057</t>
+          <t>1075222</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1183208</t>
+          <t>1188671</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2035267</t>
+          <t>2046868</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2189962</t>
+          <t>2201732</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,74%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>750066</t>
+          <t>749059</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>849414</t>
+          <t>850435</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>593304</t>
+          <t>592955</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>682349</t>
+          <t>687184</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1373765</t>
+          <t>1371472</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1502213</t>
+          <t>1505198</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>79853</t>
+          <t>79747</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>121100</t>
+          <t>118710</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>47090</t>
+          <t>47434</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>82087</t>
+          <t>81347</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>137227</t>
+          <t>135125</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>190752</t>
+          <t>188324</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>211477</t>
+          <t>213809</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>271939</t>
+          <t>275886</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>102033</t>
+          <t>100732</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>147227</t>
+          <t>148405</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>326986</t>
+          <t>329209</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>402720</t>
+          <t>404290</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces que se cepilla los dientes al día en 2023</t>
+          <t>Población según el número de veces que se cepilla los dientes al día en 2023 (tasa de respuesta: 99,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36171</t>
+          <t>36509</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61607</t>
+          <t>60573</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>117787</t>
+          <t>116349</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>152281</t>
+          <t>153840</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>161399</t>
+          <t>160614</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>209496</t>
+          <t>205085</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>191827</t>
+          <t>193328</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>233540</t>
+          <t>234766</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>319473</t>
+          <t>321968</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>360361</t>
+          <t>362734</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>520227</t>
+          <t>522687</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>583141</t>
+          <t>582691</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,77%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>147240</t>
+          <t>146403</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>187040</t>
+          <t>184213</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>175578</t>
+          <t>174619</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>210963</t>
+          <t>209430</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>333060</t>
+          <t>334768</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>386749</t>
+          <t>389675</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,28%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21332</t>
+          <t>21363</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39789</t>
+          <t>40676</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17405</t>
+          <t>17472</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31789</t>
+          <t>32034</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42952</t>
+          <t>43561</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66683</t>
+          <t>67172</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40078</t>
+          <t>40047</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63894</t>
+          <t>64854</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38693</t>
+          <t>38183</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>58134</t>
+          <t>57517</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4192,39 +4192,39 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>7,79%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>98097</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>83763</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>114129</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t>7,87%</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>98097</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>83722</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>114408</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>7,87%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
           <t>6,72%</t>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>474235</t>
+          <t>474600</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1164458</t>
+          <t>1270411</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>493539</t>
+          <t>477765</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>751076</t>
+          <t>750861</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1103964</t>
+          <t>1103428</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1914159</t>
+          <t>1942975</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>43,0%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>790205</t>
+          <t>748326</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1279239</t>
+          <t>1281433</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1205094</t>
+          <t>1204261</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1560382</t>
+          <t>1574749</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2057374</t>
+          <t>2045378</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2691458</t>
+          <t>2716476</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>60,11%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>288296</t>
+          <t>264636</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>469122</t>
+          <t>470753</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>155683</t>
+          <t>155579</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>248939</t>
+          <t>252895</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>495822</t>
+          <t>485557</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>694956</t>
+          <t>699445</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>9821</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24655</t>
+          <t>26251</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6799</t>
+          <t>6660</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20402</t>
+          <t>20582</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18824</t>
+          <t>18641</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39325</t>
+          <t>38640</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35619</t>
+          <t>36708</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>72524</t>
+          <t>72551</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18220</t>
+          <t>17870</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39963</t>
+          <t>39044</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>61467</t>
+          <t>62400</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>102020</t>
+          <t>103945</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>205940</t>
+          <t>202560</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>255647</t>
+          <t>253828</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>283872</t>
+          <t>284283</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>327962</t>
+          <t>328758</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>502170</t>
+          <t>499250</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>570854</t>
+          <t>569031</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,58%</t>
         </is>
       </c>
     </row>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>287509</t>
+          <t>285881</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>341094</t>
+          <t>341790</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>284777</t>
+          <t>283773</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>329141</t>
+          <t>327810</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>585323</t>
+          <t>583138</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>653356</t>
+          <t>655408</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>50,19%</t>
         </is>
       </c>
     </row>
@@ -5280,12 +5280,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>80835</t>
+          <t>83334</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>129960</t>
+          <t>133162</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33673</t>
+          <t>33559</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>54842</t>
+          <t>54601</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>122578</t>
+          <t>120440</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>176953</t>
+          <t>175995</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6398</t>
+          <t>6069</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>556</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5995</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1578</t>
+          <t>1574</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8417</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>3530</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>475</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5723</t>
+          <t>5832</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>773</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>6763</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>747370</t>
+          <t>749160</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1541024</t>
+          <t>1530246</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>886113</t>
+          <t>904797</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1194523</t>
+          <t>1198441</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1818260</t>
+          <t>1815389</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2591091</t>
+          <t>2684778</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>37,97%</t>
         </is>
       </c>
     </row>
@@ -5849,12 +5849,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1271794</t>
+          <t>1277392</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1799670</t>
+          <t>1800426</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5864,12 +5864,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1844907</t>
+          <t>1839260</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2301310</t>
+          <t>2285862</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3306636</t>
+          <t>3241843</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3934500</t>
+          <t>3928181</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>55,56%</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5962,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>530015</t>
+          <t>519065</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>750730</t>
+          <t>748486</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5977,12 +5977,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>371832</t>
+          <t>371000</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>495774</t>
+          <t>496005</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>959424</t>
+          <t>971937</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1210599</t>
+          <t>1219026</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>35367</t>
+          <t>35254</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>61107</t>
+          <t>62615</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>28254</t>
+          <t>28876</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>49052</t>
+          <t>50378</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>69449</t>
+          <t>68870</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>103130</t>
+          <t>104675</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>79759</t>
+          <t>82071</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>128858</t>
+          <t>128063</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>61033</t>
+          <t>59480</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>92206</t>
+          <t>94442</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>153624</t>
+          <t>155460</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>211606</t>
+          <t>211558</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">

--- a/data/trans_orig/P19E-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P19E-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>137871</t>
+          <t>137160</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>179993</t>
+          <t>181775</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>245809</t>
+          <t>246458</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>303897</t>
+          <t>300540</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>394249</t>
+          <t>396668</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>468606</t>
+          <t>470782</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,28%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>157363</t>
+          <t>158403</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>204521</t>
+          <t>202849</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>268290</t>
+          <t>267234</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>327803</t>
+          <t>328652</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>437652</t>
+          <t>438943</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>513448</t>
+          <t>512793</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,8%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>192708</t>
+          <t>193576</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>240558</t>
+          <t>242992</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>219366</t>
+          <t>219113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>274151</t>
+          <t>277179</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>431145</t>
+          <t>424965</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>506276</t>
+          <t>501251</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,11%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33998</t>
+          <t>33543</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59622</t>
+          <t>57990</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31861</t>
+          <t>31847</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58948</t>
+          <t>60489</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>71239</t>
+          <t>70850</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110579</t>
+          <t>108307</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94074</t>
+          <t>94859</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>133826</t>
+          <t>132929</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71246</t>
+          <t>72616</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>109978</t>
+          <t>108733</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>177476</t>
+          <t>178104</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>230813</t>
+          <t>231078</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>674889</t>
+          <t>674059</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>762645</t>
+          <t>764979</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>836611</t>
+          <t>833252</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>923280</t>
+          <t>925670</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1536235</t>
+          <t>1537086</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1663348</t>
+          <t>1661876</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,8%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>610899</t>
+          <t>610626</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>694688</t>
+          <t>693405</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>638461</t>
+          <t>637476</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>722542</t>
+          <t>725494</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1272247</t>
+          <t>1278136</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1389627</t>
+          <t>1394864</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,08%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>449304</t>
+          <t>449870</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>529050</t>
+          <t>526914</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>309050</t>
+          <t>308112</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>379182</t>
+          <t>379330</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>782187</t>
+          <t>773440</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>881785</t>
+          <t>882341</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33787</t>
+          <t>35667</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62461</t>
+          <t>64370</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>10582</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29875</t>
+          <t>30914</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49947</t>
+          <t>50911</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85709</t>
+          <t>83154</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101033</t>
+          <t>100538</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>146676</t>
+          <t>147352</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19031</t>
+          <t>18020</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40378</t>
+          <t>41283</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>126356</t>
+          <t>125729</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>178225</t>
+          <t>176421</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>253826</t>
+          <t>255344</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>304289</t>
+          <t>303598</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>310419</t>
+          <t>311850</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>357080</t>
+          <t>357011</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>577582</t>
+          <t>582412</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>646764</t>
+          <t>647823</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,78%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>131284</t>
+          <t>131231</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>174836</t>
+          <t>173744</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>131419</t>
+          <t>133347</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>175247</t>
+          <t>175904</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>275645</t>
+          <t>274270</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>336406</t>
+          <t>334281</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,85%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>78101</t>
+          <t>78070</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>115222</t>
+          <t>117847</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38624</t>
+          <t>39991</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>66774</t>
+          <t>67803</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>124950</t>
+          <t>125957</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>170365</t>
+          <t>173807</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12771</t>
+          <t>13155</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13181</t>
+          <t>14004</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3169</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15738</t>
+          <t>16003</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11448</t>
+          <t>11485</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7136</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23043</t>
+          <t>23097</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1097780</t>
+          <t>1096791</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1208958</t>
+          <t>1210073</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1426649</t>
+          <t>1430394</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1542506</t>
+          <t>1546838</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2557344</t>
+          <t>2559551</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2724260</t>
+          <t>2724502</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,52%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>935033</t>
+          <t>930866</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1036217</t>
+          <t>1041696</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1075222</t>
+          <t>1075237</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1188671</t>
+          <t>1181645</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2046868</t>
+          <t>2041590</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2201732</t>
+          <t>2200960</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>749059</t>
+          <t>751938</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>850435</t>
+          <t>850388</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>592955</t>
+          <t>591296</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>687184</t>
+          <t>685119</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1371472</t>
+          <t>1372983</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1505198</t>
+          <t>1506600</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,4%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>79747</t>
+          <t>79307</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>118710</t>
+          <t>118171</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>47434</t>
+          <t>47469</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>81347</t>
+          <t>81375</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>135125</t>
+          <t>133834</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>188324</t>
+          <t>187514</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>213809</t>
+          <t>211119</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>275886</t>
+          <t>271610</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>100732</t>
+          <t>102155</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>148405</t>
+          <t>146865</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>329209</t>
+          <t>332984</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>404290</t>
+          <t>405635</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -3685,32 +3685,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>47648</t>
+          <t>56283</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36509</t>
+          <t>43935</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60573</t>
+          <t>73825</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3720,32 +3720,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>133919</t>
+          <t>144464</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>116349</t>
+          <t>128483</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>153840</t>
+          <t>163995</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3755,32 +3755,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>181567</t>
+          <t>200747</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>160614</t>
+          <t>178613</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>205085</t>
+          <t>224027</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -3798,32 +3798,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>212984</t>
+          <t>242936</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>193328</t>
+          <t>219465</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>234766</t>
+          <t>266653</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3833,32 +3833,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>340495</t>
+          <t>377436</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>321968</t>
+          <t>355414</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>362734</t>
+          <t>399607</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3868,32 +3868,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>553479</t>
+          <t>620373</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>522687</t>
+          <t>587447</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>582691</t>
+          <t>652173</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>47,43%</t>
         </is>
       </c>
     </row>
@@ -3911,32 +3911,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>166649</t>
+          <t>186045</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>146403</t>
+          <t>166799</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>184213</t>
+          <t>208502</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3946,32 +3946,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>192670</t>
+          <t>206504</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>174619</t>
+          <t>187256</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>209430</t>
+          <t>225961</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3981,32 +3981,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>359319</t>
+          <t>392549</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>334768</t>
+          <t>365257</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>389675</t>
+          <t>420005</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>30,55%</t>
         </is>
       </c>
     </row>
@@ -4024,32 +4024,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29568</t>
+          <t>31512</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21363</t>
+          <t>22228</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40676</t>
+          <t>42403</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4059,32 +4059,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23845</t>
+          <t>28022</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17472</t>
+          <t>20650</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32034</t>
+          <t>36443</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4094,32 +4094,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>53413</t>
+          <t>59534</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43561</t>
+          <t>47192</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67172</t>
+          <t>74292</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -4137,32 +4137,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>50306</t>
+          <t>53016</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40047</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64854</t>
+          <t>66464</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4172,32 +4172,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>47792</t>
+          <t>48797</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38183</t>
+          <t>40365</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>57517</t>
+          <t>60868</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4207,32 +4207,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>98097</t>
+          <t>101813</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>83763</t>
+          <t>86741</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>114129</t>
+          <t>118785</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -4250,17 +4250,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>507155</t>
+          <t>569792</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>507155</t>
+          <t>569792</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>507155</t>
+          <t>569792</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4285,17 +4285,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>738721</t>
+          <t>805223</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>738721</t>
+          <t>805223</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>738721</t>
+          <t>805223</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4320,17 +4320,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1245876</t>
+          <t>1375015</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1245876</t>
+          <t>1375015</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1245876</t>
+          <t>1375015</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4367,32 +4367,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>683060</t>
+          <t>495611</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>474600</t>
+          <t>447421</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1270411</t>
+          <t>547214</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4402,32 +4402,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>651333</t>
+          <t>695238</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>477765</t>
+          <t>653567</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>750861</t>
+          <t>737550</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4437,32 +4437,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1334393</t>
+          <t>1190850</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1103428</t>
+          <t>1120135</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1942975</t>
+          <t>1249857</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>28,48%</t>
         </is>
       </c>
     </row>
@@ -4480,32 +4480,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1125399</t>
+          <t>1215379</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>748326</t>
+          <t>1159868</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1281433</t>
+          <t>1271490</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4515,32 +4515,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1330858</t>
+          <t>1190008</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1204261</t>
+          <t>1144263</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1574749</t>
+          <t>1235002</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4550,32 +4550,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2456257</t>
+          <t>2405387</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2045378</t>
+          <t>2341022</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2716476</t>
+          <t>2480398</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>56,51%</t>
         </is>
       </c>
     </row>
@@ -4593,32 +4593,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>405806</t>
+          <t>437238</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>264636</t>
+          <t>400312</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>470753</t>
+          <t>481418</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4628,32 +4628,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212717</t>
+          <t>239969</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>155579</t>
+          <t>213358</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>252895</t>
+          <t>268758</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4663,32 +4663,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>618523</t>
+          <t>677207</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>485557</t>
+          <t>630780</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>699445</t>
+          <t>725018</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -4706,32 +4706,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15964</t>
+          <t>18479</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9821</t>
+          <t>11168</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26251</t>
+          <t>28778</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4741,27 +4741,27 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12171</t>
+          <t>12784</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6660</t>
+          <t>7553</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20582</t>
+          <t>20034</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -4776,32 +4776,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>28135</t>
+          <t>31264</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18641</t>
+          <t>22675</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38640</t>
+          <t>44184</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -4819,32 +4819,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>54257</t>
+          <t>55687</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36708</t>
+          <t>42529</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>72551</t>
+          <t>72962</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4854,32 +4854,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>27504</t>
+          <t>28870</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17870</t>
+          <t>21122</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39044</t>
+          <t>39525</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4889,32 +4889,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>81762</t>
+          <t>84557</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>62400</t>
+          <t>67085</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>103945</t>
+          <t>103679</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -4932,17 +4932,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2284486</t>
+          <t>2222394</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2284486</t>
+          <t>2222394</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2284486</t>
+          <t>2222394</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4967,17 +4967,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2234584</t>
+          <t>2166870</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2234584</t>
+          <t>2166870</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2234584</t>
+          <t>2166870</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5002,17 +5002,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4519070</t>
+          <t>4389264</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4519070</t>
+          <t>4389264</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4519070</t>
+          <t>4389264</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5049,32 +5049,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>228992</t>
+          <t>264187</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>202560</t>
+          <t>237140</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>253828</t>
+          <t>293024</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5084,32 +5084,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>305538</t>
+          <t>337520</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>284283</t>
+          <t>311774</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>328758</t>
+          <t>363212</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5119,32 +5119,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>534530</t>
+          <t>601708</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>499250</t>
+          <t>568209</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>569031</t>
+          <t>638043</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>44,15%</t>
         </is>
       </c>
     </row>
@@ -5162,32 +5162,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>312910</t>
+          <t>343852</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>285881</t>
+          <t>311642</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>341790</t>
+          <t>372679</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5197,32 +5197,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>307000</t>
+          <t>341185</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>283773</t>
+          <t>316553</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>327810</t>
+          <t>365404</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5232,32 +5232,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>619910</t>
+          <t>685037</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>583138</t>
+          <t>646856</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>655408</t>
+          <t>719117</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>49,76%</t>
         </is>
       </c>
     </row>
@@ -5275,32 +5275,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>101430</t>
+          <t>98678</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>83334</t>
+          <t>80860</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>133162</t>
+          <t>122737</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5310,32 +5310,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>43056</t>
+          <t>51116</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33559</t>
+          <t>40686</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>54601</t>
+          <t>67679</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5345,32 +5345,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>144487</t>
+          <t>149794</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>120440</t>
+          <t>126884</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>175995</t>
+          <t>176031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6069</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -5423,22 +5423,22 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2263</t>
+          <t>2361</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>612</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5812</t>
+          <t>5807</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5458,22 +5458,22 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8484</t>
+          <t>9504</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -5511,92 +5511,92 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3530</t>
+          <t>9469</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2122</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>4352</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>1544</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>12298</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>0,11%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>2043</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>475</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>5832</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>2784</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>773</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>6763</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -5614,17 +5614,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>645885</t>
+          <t>710861</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>645885</t>
+          <t>710861</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>645885</t>
+          <t>710861</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5649,17 +5649,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>659899</t>
+          <t>734305</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>659899</t>
+          <t>734305</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>659899</t>
+          <t>734305</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5684,17 +5684,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1305784</t>
+          <t>1445166</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1305784</t>
+          <t>1445166</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1305784</t>
+          <t>1445166</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5731,32 +5731,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>959700</t>
+          <t>816081</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>749160</t>
+          <t>767316</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1530246</t>
+          <t>872746</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5766,32 +5766,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1090790</t>
+          <t>1177223</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>904797</t>
+          <t>1124500</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1198441</t>
+          <t>1229466</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5801,32 +5801,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2050490</t>
+          <t>1993304</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1815389</t>
+          <t>1915593</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2684778</t>
+          <t>2070269</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -5844,32 +5844,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1651293</t>
+          <t>1802167</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1277392</t>
+          <t>1728067</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1800426</t>
+          <t>1859996</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5879,32 +5879,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1978353</t>
+          <t>1908629</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1839260</t>
+          <t>1854259</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2285862</t>
+          <t>1962123</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5914,32 +5914,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3629646</t>
+          <t>3710795</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3241843</t>
+          <t>3621315</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3928181</t>
+          <t>3788438</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>52,55%</t>
         </is>
       </c>
     </row>
@@ -5957,32 +5957,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>673886</t>
+          <t>721961</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>519065</t>
+          <t>667969</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>748486</t>
+          <t>773831</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5992,32 +5992,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>448443</t>
+          <t>497589</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>371000</t>
+          <t>464097</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>496005</t>
+          <t>536917</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6027,32 +6027,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1122329</t>
+          <t>1219550</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>971937</t>
+          <t>1161526</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1219026</t>
+          <t>1283457</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -6070,32 +6070,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>47343</t>
+          <t>51905</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>35254</t>
+          <t>38774</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>62615</t>
+          <t>66584</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6105,32 +6105,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>38279</t>
+          <t>43168</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>28876</t>
+          <t>33289</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50378</t>
+          <t>54030</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6140,32 +6140,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>85623</t>
+          <t>95073</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>68870</t>
+          <t>78744</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>104675</t>
+          <t>114117</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -6183,32 +6183,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>105304</t>
+          <t>110932</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>82071</t>
+          <t>92199</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>128063</t>
+          <t>134659</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6218,32 +6218,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>77339</t>
+          <t>79789</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>59480</t>
+          <t>65662</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>94442</t>
+          <t>94198</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6253,32 +6253,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>182643</t>
+          <t>190722</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>155460</t>
+          <t>167033</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>211558</t>
+          <t>217232</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -6296,17 +6296,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3437526</t>
+          <t>3503046</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3437526</t>
+          <t>3503046</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3437526</t>
+          <t>3503046</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6331,17 +6331,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3633204</t>
+          <t>3706398</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3633204</t>
+          <t>3706398</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3633204</t>
+          <t>3706398</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6366,17 +6366,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7070730</t>
+          <t>7209444</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7070730</t>
+          <t>7209444</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7070730</t>
+          <t>7209444</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
